--- a/CHITIEU/INPUT/TW.xlsx
+++ b/CHITIEU/INPUT/TW.xlsx
@@ -10908,11 +10908,9 @@
       </c>
       <c r="D100" s="22">
         <f>SUM(D3:D99)</f>
-        <v>0</v>
       </c>
       <c r="E100" s="22">
         <f t="shared" ref="E100:AA100" si="10">SUM(E3:E99)</f>
-        <v>0</v>
       </c>
       <c r="F100" s="22">
         <v>0</v>
@@ -11158,7 +11156,7 @@
       <c r="G103" s="25"/>
       <c r="H103" s="25">
         <f>E99+H99+K99+AF99+W99+N99+Z99+Q99+T99+AC99+AI99+#REF!+AL99+AO99+AR99+AU99</f>
-        <v>#REF!</v>
+        <v>0</v>
       </c>
       <c r="I103" s="25"/>
       <c r="J103" s="25"/>
